--- a/Catch models/quantis_btk_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_btk_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.1352920128019947</v>
+        <v>0.0495729066682501</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.2905227629478898</v>
+        <v>0.139697318064088</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.428032882757397</v>
+        <v>0.2999272327930735</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.544391780550795</v>
+        <v>0.475350178159304</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.747448081069701</v>
+        <v>0.7853982067094842</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_btk_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.0495729066682501</v>
+        <v>0.06455074667988407</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.139697318064088</v>
+        <v>0.156229148708264</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.2999272327930735</v>
+        <v>0.254382820785497</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.475350178159304</v>
+        <v>0.382660056416632</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.7853982067094842</v>
+        <v>0.7561127434898981</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_btk_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.06455074667988407</v>
+        <v>0.0596058487932849</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.156229148708264</v>
+        <v>0.146090336033906</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.254382820785497</v>
+        <v>0.235700491772678</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.382660056416632</v>
+        <v>0.367102326260825</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.7561127434898981</v>
+        <v>0.7783292760537105</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_btk_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.0596058487932849</v>
+        <v>0.0614562737019877</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.146090336033906</v>
+        <v>0.150272045894028</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.235700491772678</v>
+        <v>0.2285014946706645</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.367102326260825</v>
+        <v>0.333612199898818</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.7783292760537105</v>
+        <v>0.6325944967135561</v>
       </c>
     </row>
   </sheetData>
